--- a/outputs/global_xlsx/global_market_20260612.xlsx
+++ b/outputs/global_xlsx/global_market_20260612.xlsx
@@ -643,11 +643,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>69160</v>
+        <v>69593.64</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.76%</t>
+          <t>5.41%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -668,11 +668,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8596.57</v>
+        <v>8563.469999999999</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5.82%</t>
+          <t>5.41%</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -693,16 +693,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>44169.04</v>
+        <v>45256.24</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.46%</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>06/12</t>
+          <t>06/15</t>
         </is>
       </c>
     </row>
@@ -718,16 +718,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24718.1</v>
+        <v>24835.77</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>06/12</t>
+          <t>06/15</t>
         </is>
       </c>
     </row>
@@ -743,16 +743,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4777.32</v>
+        <v>4844.47</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>06/12</t>
+          <t>06/15</t>
         </is>
       </c>
     </row>
@@ -768,11 +768,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8929.5</v>
+        <v>8922.700000000001</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -818,11 +818,11 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4317.5</v>
+        <v>4356.7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>3.36%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>80.98999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-4.58%</t>
+          <t>-5.63%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -868,11 +868,11 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.53</v>
+        <v>6.56</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -893,11 +893,11 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>70.43000000000001</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3.79%</t>
+          <t>4.37%</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -918,11 +918,11 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1130.75</v>
+        <v>1133.75</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -943,11 +943,11 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>409.5</v>
+        <v>409.75</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-0.79%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -968,11 +968,11 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>578.75</v>
+        <v>580.25</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-0.98%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1018,11 +1018,11 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>65510.73</v>
+        <v>65394.82</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.51%</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1043,11 +1043,11 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>31.53</v>
+        <v>31.52</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1118,11 +1118,11 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>160.03</v>
+        <v>160.14</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1143,11 +1143,11 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>99.48999999999999</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
